--- a/word-lists/100-wordlist-Dutch.xlsx
+++ b/word-lists/100-wordlist-Dutch.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\KDrive\Project\Keyboard\keyboard heaven - in work\KeyDual Github readme\Claude word list docs and files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\KDrive\Project\Keyboard\keyboard heaven - in work\KeyDual Github readme\Wordlist 2026-04-20 files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9F883AC-E71B-4972-8DD8-623685865C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{07AEC3C0-B1DD-4E0F-B8F4-AB72CA03B5C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5649" yWindow="2049" windowWidth="24685" windowHeight="13054" xr2:uid="{DD400BA7-562A-4AD5-AF53-2FC852384BB5}"/>
+    <workbookView xWindow="5649" yWindow="2049" windowWidth="24685" windowHeight="13054" xr2:uid="{D4EFB42A-A28A-4A33-8C0F-4B9A840EBB39}"/>
   </bookViews>
   <sheets>
     <sheet name="100-wordlist-Dutch" sheetId="1" r:id="rId1"/>
@@ -318,7 +318,7 @@
     <t>weten</t>
   </si>
   <si>
-    <t>anders</t>
+    <t>verschillende</t>
   </si>
   <si>
     <t>belangrijk</t>
@@ -330,7 +330,7 @@
     <t>regering</t>
   </si>
   <si>
-    <t>vraag</t>
+    <t>beschikbaar</t>
   </si>
   <si>
     <t>voorbeeld</t>
@@ -1193,7 +1193,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6955EAE8-8686-479D-B872-14853DCCCF9F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E9AAA7D-44A4-4EE4-9904-D98406BCA8E1}">
   <dimension ref="A1:C101"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
